--- a/data/influencer_dataset.xlsx
+++ b/data/influencer_dataset.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O89"/>
+  <dimension ref="A1:O92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -831,7 +831,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Fastapi, Python</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Fastapi</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -1374,7 +1374,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Dev Branch</t>
+          <t>Gate Smashers</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1384,15 +1384,15 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@devbranchdev</t>
+          <t>https://www.youtube.com/@GateSmashers</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>2567940</v>
+        <v>2870000</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Flutter mobile developer</t>
+          <t>Fastapi, AI</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1412,8 +1412,16 @@
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>18-34</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
       <c r="M16" t="inlineStr">
         <is>
           <t>Global</t>
@@ -1426,14 +1434,14 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>Subscribers/Followers (2,567,940) exceeds micro-influencer ceiling of 100,000 (Macro tier)</t>
+          <t>Subscribers/Followers (2,870,000) exceeds micro-influencer ceiling of 100,000 (Macro tier) | Engagement rate (1.5%) is below minimum healthy baseline of 2.0%</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>David Bombal</t>
+          <t>Dev Branch</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1443,15 +1451,15 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@davidbombal</t>
+          <t>https://www.youtube.com/@devbranchdev</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>2450000</v>
+        <v>2567940</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1461,37 +1469,21 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Cybersecurity, Networking, Python for Hackers, Linux</t>
+          <t>Flutter mobile developer</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>david@bombal.com</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>@davidbombal</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>https://davidbombal.com</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>18-45</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>89% Male, 11% Female</t>
-        </is>
-      </c>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
-          <t>US / UK / Global</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1501,14 +1493,14 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>Subscribers/Followers (2,450,000) exceeds micro-influencer ceiling of 100,000 (Macro tier)</t>
+          <t>Subscribers/Followers (2,567,940) exceeds micro-influencer ceiling of 100,000 (Macro tier)</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Venom's Tech</t>
+          <t>David Bombal</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1518,15 +1510,15 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@VenomsTech</t>
+          <t>https://www.youtube.com/@davidbombal</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1630000</v>
+        <v>2450000</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>3.9%</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1536,21 +1528,37 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Tech</t>
+          <t>Cybersecurity, Networking, Python for Hackers, Linux</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Not Found</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr"/>
+          <t>david@bombal.com</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>@davidbombal</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>https://davidbombal.com</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>18-45</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>89% Male, 11% Female</t>
+        </is>
+      </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>US / UK / Global</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1560,14 +1568,14 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>Subscribers/Followers (1,630,000) exceeds micro-influencer ceiling of 100,000 (Macro tier) | Engagement rate (1.5%) is below minimum healthy baseline of 2.0%</t>
+          <t>Subscribers/Followers (2,450,000) exceeds micro-influencer ceiling of 100,000 (Macro tier)</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>codebasics</t>
+          <t>Tech With Tim</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1577,11 +1585,11 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@codebasics</t>
+          <t>https://www.youtube.com/@TechWithTim</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1580000</v>
+        <v>2089999</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1595,18 +1603,26 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Langchain, AI</t>
+          <t>Fastapi</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>business@codebasics.io</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr"/>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>18-34</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
       <c r="M19" t="inlineStr">
         <is>
           <t>Global</t>
@@ -1619,14 +1635,14 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>Subscribers/Followers (1,580,000) exceeds micro-influencer ceiling of 100,000 (Macro tier) | Engagement rate (1.5%) is below minimum healthy baseline of 2.0%</t>
+          <t>Subscribers/Followers (2,089,999) exceeds micro-influencer ceiling of 100,000 (Macro tier) | Engagement rate (1.5%) is below minimum healthy baseline of 2.0%</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Krish Naik</t>
+          <t>Venom's Tech</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1636,11 +1652,11 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@krishnaik06</t>
+          <t>https://www.youtube.com/@VenomsTech</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1510000</v>
+        <v>1630000</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1654,12 +1670,12 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Langchain, AI</t>
+          <t>Tech</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>krishnaik06@gmail.com</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -1678,14 +1694,14 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>Subscribers/Followers (1,510,000) exceeds micro-influencer ceiling of 100,000 (Macro tier) | Engagement rate (1.5%) is below minimum healthy baseline of 2.0%</t>
+          <t>Subscribers/Followers (1,630,000) exceeds micro-influencer ceiling of 100,000 (Macro tier) | Engagement rate (1.5%) is below minimum healthy baseline of 2.0%</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Chai aur Code</t>
+          <t>codebasics</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1695,11 +1711,11 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@chaiaurcode</t>
+          <t>https://www.youtube.com/@codebasics</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>940000</v>
+        <v>1580000</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1713,12 +1729,12 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Langchain, AI</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>team@hiteshchoudhary.com</t>
+          <t>business@codebasics.io</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -1737,14 +1753,14 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>Subscribers/Followers (940,000) exceeds micro-influencer ceiling of 100,000 (Macro tier) | Engagement rate (1.5%) is below minimum healthy baseline of 2.0%</t>
+          <t>Subscribers/Followers (1,580,000) exceeds micro-influencer ceiling of 100,000 (Macro tier) | Engagement rate (1.5%) is below minimum healthy baseline of 2.0%</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>CampusX</t>
+          <t>Krish Naik</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1754,11 +1770,11 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@campusx-official</t>
+          <t>https://www.youtube.com/@krishnaik06</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>737000</v>
+        <v>1510000</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1777,7 +1793,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>support@campusx.in</t>
+          <t>krishnaik06@gmail.com</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -1796,14 +1812,14 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>Subscribers/Followers (737,000) exceeds micro-influencer ceiling of 100,000 (Macro tier) | Engagement rate (1.5%) is below minimum healthy baseline of 2.0%</t>
+          <t>Subscribers/Followers (1,510,000) exceeds micro-influencer ceiling of 100,000 (Macro tier) | Engagement rate (1.5%) is below minimum healthy baseline of 2.0%</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Your Average Tech Bro</t>
+          <t>Chai aur Code</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1813,15 +1829,15 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@YourAverageTechBro</t>
+          <t>https://www.youtube.com/@chaiaurcode</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>673087</v>
+        <v>941000</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1831,18 +1847,26 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Flutter mobile developer</t>
+          <t>Fastapi, AI</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>team@hiteshchoudhary.com</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>18-34</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
       <c r="M23" t="inlineStr">
         <is>
           <t>Global</t>
@@ -1855,14 +1879,14 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>Subscribers/Followers (673,087) exceeds micro-influencer ceiling of 100,000 (Macro tier)</t>
+          <t>Subscribers/Followers (941,000) exceeds micro-influencer ceiling of 100,000 (Macro tier) | Engagement rate (1.5%) is below minimum healthy baseline of 2.0%</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Neat Roots</t>
+          <t>Caleb Curry</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1872,15 +1896,15 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@NeatRoots</t>
+          <t>https://www.youtube.com/@codebreakthrough</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>584725</v>
+        <v>743000</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1890,18 +1914,26 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Flutter mobile developer</t>
+          <t>Fastapi</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>calebcurry@kernelmanagement.com</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>18-34</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr">
         <is>
           <t>Global</t>
@@ -1914,14 +1946,14 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>Subscribers/Followers (584,725) exceeds micro-influencer ceiling of 100,000 (Macro tier)</t>
+          <t>Subscribers/Followers (743,000) exceeds micro-influencer ceiling of 100,000 (Macro tier) | Engagement rate (1.5%) is below minimum healthy baseline of 2.0%</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Flutter</t>
+          <t>CampusX</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1931,15 +1963,15 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@flutterdev</t>
+          <t>https://www.youtube.com/@campusx-official</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>546495</v>
+        <v>737000</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>18.0%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1949,12 +1981,12 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Flutter mobile developer</t>
+          <t>Langchain, AI</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>support@campusx.in</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -1973,14 +2005,14 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>Subscribers/Followers (546,495) exceeds micro-influencer ceiling of 100,000 (Macro tier)</t>
+          <t>Subscribers/Followers (737,000) exceeds micro-influencer ceiling of 100,000 (Macro tier) | Engagement rate (1.5%) is below minimum healthy baseline of 2.0%</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data with Baraa</t>
+          <t>Your Average Tech Bro</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1990,15 +2022,15 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@DataWithBaraa</t>
+          <t>https://www.youtube.com/@YourAverageTechBro</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>497000</v>
+        <v>673087</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -2008,7 +2040,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Flutter mobile developer</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
@@ -2018,16 +2050,8 @@
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>18-34</t>
-        </is>
-      </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>Mixed</t>
-        </is>
-      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
           <t>Global</t>
@@ -2040,14 +2064,14 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>Subscribers/Followers (497,000) exceeds micro-influencer ceiling of 100,000 (Macro tier) | Engagement rate (1.5%) is below minimum healthy baseline of 2.0%</t>
+          <t>Subscribers/Followers (673,087) exceeds micro-influencer ceiling of 100,000 (Macro tier)</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Indently</t>
+          <t>Neat Roots</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2057,15 +2081,15 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@Indently</t>
+          <t>https://www.youtube.com/@NeatRoots</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>367000</v>
+        <v>584725</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -2075,7 +2099,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Python</t>
+          <t>Flutter mobile developer</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -2085,16 +2109,8 @@
       </c>
       <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr">
-        <is>
-          <t>18-34</t>
-        </is>
-      </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>Mixed</t>
-        </is>
-      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>Global</t>
@@ -2107,14 +2123,14 @@
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>Subscribers/Followers (367,000) exceeds micro-influencer ceiling of 100,000 (Macro tier) | Engagement rate (1.5%) is below minimum healthy baseline of 2.0%</t>
+          <t>Subscribers/Followers (584,725) exceeds micro-influencer ceiling of 100,000 (Macro tier)</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>WsCube AI &amp; Tech School</t>
+          <t>Flutter</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2124,11 +2140,11 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@wscubeaiandtechschool</t>
+          <t>https://www.youtube.com/@flutterdev</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>310835</v>
+        <v>546495</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -2166,14 +2182,14 @@
       </c>
       <c r="O28" t="inlineStr">
         <is>
-          <t>Subscribers/Followers (310,835) exceeds micro-influencer ceiling of 100,000 (Macro tier)</t>
+          <t>Subscribers/Followers (546,495) exceeds micro-influencer ceiling of 100,000 (Macro tier)</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Krish Naik Hindi</t>
+          <t>Coding With Sagar</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2183,11 +2199,11 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@krishnaikhindi</t>
+          <t>https://www.youtube.com/@codingwithsagarcw</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>185000</v>
+        <v>511000</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -2201,7 +2217,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Langchain, AI</t>
+          <t>Fastapi, Machine Learning</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -2211,8 +2227,16 @@
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>18-34</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
       <c r="M29" t="inlineStr">
         <is>
           <t>Global</t>
@@ -2225,14 +2249,14 @@
       </c>
       <c r="O29" t="inlineStr">
         <is>
-          <t>Subscribers/Followers (185,000) exceeds micro-influencer ceiling of 100,000 (Macro tier) | Engagement rate (1.5%) is below minimum healthy baseline of 2.0%</t>
+          <t>Subscribers/Followers (511,000) exceeds micro-influencer ceiling of 100,000 (Macro tier) | Engagement rate (1.5%) is below minimum healthy baseline of 2.0%</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Ansh Lamba</t>
+          <t>Data with Baraa</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2242,11 +2266,11 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@AnshLambaJSR</t>
+          <t>https://www.youtube.com/@DataWithBaraa</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>155000</v>
+        <v>497000</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -2260,18 +2284,26 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Langchain, AI</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>anshlambacollab@gmail.com</t>
+          <t>Not Found</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>18-34</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
       <c r="M30" t="inlineStr">
         <is>
           <t>Global</t>
@@ -2284,14 +2316,14 @@
       </c>
       <c r="O30" t="inlineStr">
         <is>
-          <t>Subscribers/Followers (155,000) exceeds micro-influencer ceiling of 100,000 (Macro tier) | Engagement rate (1.5%) is below minimum healthy baseline of 2.0%</t>
+          <t>Subscribers/Followers (497,000) exceeds micro-influencer ceiling of 100,000 (Macro tier) | Engagement rate (1.5%) is below minimum healthy baseline of 2.0%</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sheryians AI School</t>
+          <t>Indently</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2301,11 +2333,11 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@SheryiansAI</t>
+          <t>https://www.youtube.com/@Indently</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>150000</v>
+        <v>367000</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -2351,14 +2383,14 @@
       </c>
       <c r="O31" t="inlineStr">
         <is>
-          <t>Subscribers/Followers (150,000) exceeds micro-influencer ceiling of 100,000 (Macro tier) | Engagement rate (1.5%) is below minimum healthy baseline of 2.0%</t>
+          <t>Subscribers/Followers (367,000) exceeds micro-influencer ceiling of 100,000 (Macro tier) | Engagement rate (1.5%) is below minimum healthy baseline of 2.0%</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DevasLife (Takuya Matsuyama)</t>
+          <t>WsCube AI &amp; Tech School</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2368,15 +2400,15 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@devaslife</t>
+          <t>https://www.youtube.com/@wscubeaiandtechschool</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>98200</v>
+        <v>310835</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>18.0%</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -2386,54 +2418,38 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Web Development, React Native, Indie Hacking, Vim / Neovim</t>
+          <t>Flutter mobile developer</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>contact@craftz.dog</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>@craftzdog</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>https://craftz.dog</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>20-35</t>
-        </is>
-      </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>75% Male, 25% Female</t>
-        </is>
-      </c>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Japan / US / UK</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>PASSED</t>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>Passed all criteria: Tech niche, 98,200 followers (within 5k-100k), 6.8% engagement, recently active.</t>
+          <t>Subscribers/Followers (310,835) exceeds micro-influencer ceiling of 100,000 (Macro tier)</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>The Cyber Mentor (Heath Adams)</t>
+          <t>Krish Naik Hindi</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2443,15 +2459,15 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@TCMSecurityAcademy</t>
+          <t>https://www.youtube.com/@krishnaikhindi</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>95000</v>
+        <v>185000</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -2461,54 +2477,38 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Cybersecurity, Ethical Hacking, OSINT, Penetration Testing</t>
+          <t>Langchain, AI</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>contact@tcm-sec.com</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>@thecybermentor</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>https://tcm-sec.com</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>20-40</t>
-        </is>
-      </c>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>84% Male, 16% Female</t>
-        </is>
-      </c>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>US / Canada / Germany</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>PASSED</t>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
         <is>
-          <t>Passed all criteria: Tech niche, 95,000 followers (within 5k-100k), 4.9% engagement, recently active.</t>
+          <t>Subscribers/Followers (185,000) exceeds micro-influencer ceiling of 100,000 (Macro tier) | Engagement rate (1.5%) is below minimum healthy baseline of 2.0%</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ArjanCodes</t>
+          <t>Ansh Lamba</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -2518,15 +2518,15 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@ArjanCodes</t>
+          <t>https://www.youtube.com/@AnshLambaJSR</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>92400</v>
+        <v>155000</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2536,54 +2536,38 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Python, Software Architecture, Clean Code, Design Patterns</t>
+          <t>Langchain, AI</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>info@arjancodes.com</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>@arjancodes (X/GitHub)</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>https://arjancodes.com</t>
-        </is>
-      </c>
-      <c r="K34" t="inlineStr">
-        <is>
-          <t>22-38</t>
-        </is>
-      </c>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>82% Male, 18% Female</t>
-        </is>
-      </c>
+          <t>anshlambacollab@gmail.com</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>US / Europe / India</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>PASSED</t>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
         <is>
-          <t>Passed all criteria: Tech niche, 92,400 followers (within 5k-100k), 5.4% engagement, recently active.</t>
+          <t>Subscribers/Followers (155,000) exceeds micro-influencer ceiling of 100,000 (Macro tier) | Engagement rate (1.5%) is below minimum healthy baseline of 2.0%</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>aiwithbrandon</t>
+          <t>Sheryians AI School</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -2593,11 +2577,11 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@aiwithbrandon</t>
+          <t>https://www.youtube.com/@SheryiansAI</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>89500</v>
+        <v>150000</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -2611,7 +2595,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Langchain, AI</t>
+          <t>Python</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
@@ -2621,8 +2605,16 @@
       </c>
       <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>18-34</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>Mixed</t>
+        </is>
+      </c>
       <c r="M35" t="inlineStr">
         <is>
           <t>Global</t>
@@ -2635,14 +2627,14 @@
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>Engagement rate (1.5%) is below minimum healthy baseline of 2.0%</t>
+          <t>Subscribers/Followers (150,000) exceeds micro-influencer ceiling of 100,000 (Macro tier) | Engagement rate (1.5%) is below minimum healthy baseline of 2.0%</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Code With Antonio</t>
+          <t>DevasLife (Takuya Matsuyama)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -2652,15 +2644,15 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@codewithantonio</t>
+          <t>https://www.youtube.com/@devaslife</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>89200</v>
+        <v>98200</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2670,37 +2662,37 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Full Stack, Next.js, Tailwind CSS, TypeScript, Prisma</t>
+          <t>Web Development, React Native, Indie Hacking, Vim / Neovim</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>business@codewithantonio.com</t>
+          <t>contact@craftz.dog</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>@antonio_dev</t>
+          <t>@craftzdog</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>https://codewithantonio.com</t>
+          <t>https://craftz.dog</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>18-30</t>
+          <t>20-35</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>78% Male, 22% Female</t>
+          <t>75% Male, 25% Female</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Global / US / Brazil</t>
+          <t>Japan / US / UK</t>
         </is>
       </c>
       <c r="N36" t="inlineStr">
@@ -2710,14 +2702,14 @@
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>Passed all criteria: Tech niche, 89,200 followers (within 5k-100k), 7.3% engagement, recently active.</t>
+          <t>Passed all criteria: Tech niche, 98,200 followers (within 5k-100k), 6.8% engagement, recently active.</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>NeuralNine</t>
+          <t>The Cyber Mentor (Heath Adams)</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -2727,15 +2719,15 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@NeuralNine</t>
+          <t>https://www.youtube.com/@TCMSecurityAcademy</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>87500</v>
+        <v>95000</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2745,37 +2737,37 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Python, Machine Learning, AI Automation, Algorithms</t>
+          <t>Cybersecurity, Ethical Hacking, OSINT, Penetration Testing</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>contact@neuralnine.com</t>
+          <t>contact@tcm-sec.com</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>@neuralnine</t>
+          <t>@thecybermentor</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>https://neuralnine.com</t>
+          <t>https://tcm-sec.com</t>
         </is>
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>18-34</t>
+          <t>20-40</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
         <is>
-          <t>80% Male, 20% Female</t>
+          <t>84% Male, 16% Female</t>
         </is>
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>Global / US / Germany</t>
+          <t>US / Canada / Germany</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
@@ -2785,14 +2777,14 @@
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>Passed all criteria: Tech niche, 87,500 followers (within 5k-100k), 4.8% engagement, recently active.</t>
+          <t>Passed all criteria: Tech niche, 95,000 followers (within 5k-100k), 4.9% engagement, recently active.</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>DevOps Toolkit (Viktor Farcic)</t>
+          <t>ArjanCodes</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -2802,15 +2794,15 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@DevOpsToolkit</t>
+          <t>https://www.youtube.com/@ArjanCodes</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>86000</v>
+        <v>92400</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2820,37 +2812,37 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Kubernetes, Crossplane, Cloud Native, DevOps</t>
+          <t>Python, Software Architecture, Clean Code, Design Patterns</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>viktor@farcic.com</t>
+          <t>info@arjancodes.com</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>@vfarcic</t>
+          <t>@arjancodes (X/GitHub)</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
         <is>
-          <t>https://devopstoolkitseries.com</t>
+          <t>https://arjancodes.com</t>
         </is>
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>28-45</t>
+          <t>22-38</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
         <is>
-          <t>91% Male, 9% Female</t>
+          <t>82% Male, 18% Female</t>
         </is>
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>Europe / US / Brazil</t>
+          <t>US / Europe / India</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
@@ -2860,14 +2852,14 @@
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>Passed all criteria: Tech niche, 86,000 followers (within 5k-100k), 4.1% engagement, recently active.</t>
+          <t>Passed all criteria: Tech niche, 92,400 followers (within 5k-100k), 5.4% engagement, recently active.</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SuperGamer101</t>
+          <t>aiwithbrandon</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -2877,55 +2869,39 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@SuperGamer101</t>
+          <t>https://www.youtube.com/@aiwithbrandon</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>85000</v>
+        <v>89500</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>3.2%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gaming</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Minecraft, FPS Games, Game Streams</t>
+          <t>Langchain, AI</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>sponsor@supergamer101.com</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>@supergamer101</t>
-        </is>
-      </c>
-      <c r="J39" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>13-24</t>
-        </is>
-      </c>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>80% Male, 20% Female</t>
-        </is>
-      </c>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr">
         <is>
-          <t>US / Brazil</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -2935,14 +2911,14 @@
       </c>
       <c r="O39" t="inlineStr">
         <is>
-          <t>Niche mismatch: 'Gaming' does not match target category 'Technology'</t>
+          <t>Engagement rate (1.5%) is below minimum healthy baseline of 2.0%</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Microservices Illustrated</t>
+          <t>Code With Antonio</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -2952,15 +2928,15 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@MicroservicesIllustrated</t>
+          <t>https://www.youtube.com/@codewithantonio</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>83400</v>
+        <v>89200</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>7.3%</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2970,37 +2946,37 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>System Design, Event-Driven Architecture, Kafka, Saga Pattern</t>
+          <t>Full Stack, Next.js, Tailwind CSS, TypeScript, Prisma</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>contact@microservicesillustrated.com</t>
+          <t>business@codewithantonio.com</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>@microillustrated</t>
+          <t>@antonio_dev</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>https://microservicesillustrated.com</t>
+          <t>https://codewithantonio.com</t>
         </is>
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>25-45</t>
+          <t>18-30</t>
         </is>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>86% Male, 14% Female</t>
+          <t>78% Male, 22% Female</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Global / US / India</t>
+          <t>Global / US / Brazil</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3010,14 +2986,14 @@
       </c>
       <c r="O40" t="inlineStr">
         <is>
-          <t>Passed all criteria: Tech niche, 83,400 followers (within 5k-100k), 4.9% engagement, recently active.</t>
+          <t>Passed all criteria: Tech niche, 89,200 followers (within 5k-100k), 7.3% engagement, recently active.</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Stefan Mischook</t>
+          <t>NeuralNine</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -3027,15 +3003,15 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@StefanMischook</t>
+          <t>https://www.youtube.com/@NeuralNine</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>82000</v>
+        <v>87500</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>1.2%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -3045,54 +3021,54 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Career Advice, Web Dev History, Freelancing</t>
+          <t>Python, Machine Learning, AI Automation, Algorithms</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>stefan@stefanmischook.com</t>
+          <t>contact@neuralnine.com</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>@killersites</t>
+          <t>@neuralnine</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>https://stefanmischook.com</t>
+          <t>https://neuralnine.com</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>30-50</t>
+          <t>18-34</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
         <is>
-          <t>85% Male, 15% Female</t>
+          <t>80% Male, 20% Female</t>
         </is>
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Canada / US</t>
+          <t>Global / US / Germany</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
         <is>
-          <t>FAILED</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="O41" t="inlineStr">
         <is>
-          <t>Engagement rate (1.2%) is below minimum healthy baseline of 2.0%</t>
+          <t>Passed all criteria: Tech niche, 87,500 followers (within 5k-100k), 4.8% engagement, recently active.</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Linux Mastery with Dave</t>
+          <t>DevOps Toolkit (Viktor Farcic)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -3102,15 +3078,15 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@LinuxMasteryDave</t>
+          <t>https://www.youtube.com/@DevOpsToolkit</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>78600</v>
+        <v>86000</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -3120,37 +3096,37 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Linux Administration, Bash Scripting, Vim, Server Hardening</t>
+          <t>Kubernetes, Crossplane, Cloud Native, DevOps</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>dave@linuxmastery.org</t>
+          <t>viktor@farcic.com</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>@davelinux</t>
+          <t>@vfarcic</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>https://linuxmastery.org</t>
+          <t>https://devopstoolkitseries.com</t>
         </is>
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>22-45</t>
+          <t>28-45</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>88% Male, 12% Female</t>
+          <t>91% Male, 9% Female</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>US / Germany / Brazil</t>
+          <t>Europe / US / Brazil</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3160,14 +3136,14 @@
       </c>
       <c r="O42" t="inlineStr">
         <is>
-          <t>Passed all criteria: Tech niche, 78,600 followers (within 5k-100k), 4.6% engagement, recently active.</t>
+          <t>Passed all criteria: Tech niche, 86,000 followers (within 5k-100k), 4.1% engagement, recently active.</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>James Briggs</t>
+          <t>SuperGamer101</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -3177,72 +3153,72 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@JamesBriggs</t>
+          <t>https://www.youtube.com/@SuperGamer101</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>74300</v>
+        <v>85000</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>3.2%</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Technology</t>
+          <t>Gaming</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Generative AI, Vector Databases, LangChain, LLMs, RAG</t>
+          <t>Minecraft, FPS Games, Game Streams</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>james@aurelio.ai</t>
+          <t>sponsor@supergamer101.com</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>@jamescalam (X)</t>
+          <t>@supergamer101</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>https://aurelio.ai</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>25-42</t>
+          <t>13-24</t>
         </is>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>85% Male, 15% Female</t>
+          <t>80% Male, 20% Female</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>US / UK / Canada</t>
+          <t>US / Brazil</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>PASSED</t>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
         <is>
-          <t>Passed all criteria: Tech niche, 74,300 followers (within 5k-100k), 5.1% engagement, recently active.</t>
+          <t>Niche mismatch: 'Gaming' does not match target category 'Technology'</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CloudArchitect Dan</t>
+          <t>Microservices Illustrated</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -3252,15 +3228,15 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@CloudArchitectDan</t>
+          <t>https://www.youtube.com/@MicroservicesIllustrated</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>71200</v>
+        <v>83400</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -3270,37 +3246,37 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>AWS Solutions, Well-Architected Framework, Cost Optimization</t>
+          <t>System Design, Event-Driven Architecture, Kafka, Saga Pattern</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>dan@cloudarchitectinsights.com</t>
+          <t>contact@microservicesillustrated.com</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>@dancloudarch</t>
+          <t>@microillustrated</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>https://cloudarchitectinsights.com</t>
+          <t>https://microservicesillustrated.com</t>
         </is>
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>28-48</t>
+          <t>25-45</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>87% Male, 13% Female</t>
+          <t>86% Male, 14% Female</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>US / UK / Singapore</t>
+          <t>Global / US / India</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3310,14 +3286,14 @@
       </c>
       <c r="O44" t="inlineStr">
         <is>
-          <t>Passed all criteria: Tech niche, 71,200 followers (within 5k-100k), 4.3% engagement, recently active.</t>
+          <t>Passed all criteria: Tech niche, 83,400 followers (within 5k-100k), 4.9% engagement, recently active.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Prompt Engineering (Ehsan)</t>
+          <t>Stefan Mischook</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -3327,15 +3303,15 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@PromptEngineeringChannel</t>
+          <t>https://www.youtube.com/@StefanMischook</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>69400</v>
+        <v>82000</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>1.2%</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -3345,54 +3321,54 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Prompt Engineering, Open Source LLMs, Ollama, Fine-Tuning</t>
+          <t>Career Advice, Web Dev History, Freelancing</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>promptengineering.business@gmail.com</t>
+          <t>stefan@stefanmischook.com</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>@prompt_eng</t>
+          <t>@killersites</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>https://github.com/promptengineering</t>
+          <t>https://stefanmischook.com</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>20-35</t>
+          <t>30-50</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
         <is>
-          <t>82% Male, 18% Female</t>
+          <t>85% Male, 15% Female</t>
         </is>
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>US / India / Germany</t>
+          <t>Canada / US</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>PASSED</t>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
         <is>
-          <t>Passed all criteria: Tech niche, 69,400 followers (within 5k-100k), 5.9% engagement, recently active.</t>
+          <t>Engagement rate (1.2%) is below minimum healthy baseline of 2.0%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>OpenSourcePulse</t>
+          <t>Linux Mastery with Dave</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -3402,15 +3378,15 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@OpenSourcePulse</t>
+          <t>https://www.youtube.com/@LinuxMasteryDave</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>67800</v>
+        <v>78600</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>5.0%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -3420,37 +3396,37 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Open Source, Linux, Self-Hosting, Privacy</t>
+          <t>Linux Administration, Bash Scripting, Vim, Server Hardening</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>collab@opensourcepulse.org</t>
+          <t>dave@linuxmastery.org</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>@ospulse</t>
+          <t>@davelinux</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>https://opensourcepulse.org</t>
+          <t>https://linuxmastery.org</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>23-45</t>
+          <t>22-45</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
         <is>
-          <t>87% Male, 13% Female</t>
+          <t>88% Male, 12% Female</t>
         </is>
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Germany / US / France</t>
+          <t>US / Germany / Brazil</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3460,14 +3436,14 @@
       </c>
       <c r="O46" t="inlineStr">
         <is>
-          <t>Passed all criteria: Tech niche, 67,800 followers (within 5k-100k), 5.0% engagement, recently active.</t>
+          <t>Passed all criteria: Tech niche, 78,600 followers (within 5k-100k), 4.6% engagement, recently active.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>PromptLab with Leo</t>
+          <t>James Briggs</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -3477,15 +3453,15 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@PromptLabLeo</t>
+          <t>https://www.youtube.com/@JamesBriggs</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>63900</v>
+        <v>74300</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -3495,32 +3471,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>AI Agents, CrewAI, LangGraph, Multi-Agent Systems</t>
+          <t>Generative AI, Vector Databases, LangChain, LLMs, RAG</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>leo@promptlab.ai</t>
+          <t>james@aurelio.ai</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>@promptlableo</t>
+          <t>@jamescalam (X)</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>https://promptlab.ai</t>
+          <t>https://aurelio.ai</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>21-37</t>
+          <t>25-42</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>81% Male, 19% Female</t>
+          <t>85% Male, 15% Female</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -3535,14 +3511,14 @@
       </c>
       <c r="O47" t="inlineStr">
         <is>
-          <t>Passed all criteria: Tech niche, 63,900 followers (within 5k-100k), 6.7% engagement, recently active.</t>
+          <t>Passed all criteria: Tech niche, 74,300 followers (within 5k-100k), 5.1% engagement, recently active.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>IndieDev Vlogs (Sam)</t>
+          <t>CloudArchitect Dan</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -3552,15 +3528,15 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@SamIndieDev</t>
+          <t>https://www.youtube.com/@CloudArchitectDan</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>62000</v>
+        <v>71200</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -3570,37 +3546,37 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Indie Hacking, SaaS, Next.js, Supabase, Stripe</t>
+          <t>AWS Solutions, Well-Architected Framework, Cost Optimization</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>sam@buildinpublic.xyz</t>
+          <t>dan@cloudarchitectinsights.com</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>@sambuilds</t>
+          <t>@dancloudarch</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
         <is>
-          <t>https://buildinpublic.xyz</t>
+          <t>https://cloudarchitectinsights.com</t>
         </is>
       </c>
       <c r="K48" t="inlineStr">
         <is>
-          <t>21-36</t>
+          <t>28-48</t>
         </is>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>78% Male, 22% Female</t>
+          <t>87% Male, 13% Female</t>
         </is>
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>US / UK / Netherlands</t>
+          <t>US / UK / Singapore</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3610,14 +3586,14 @@
       </c>
       <c r="O48" t="inlineStr">
         <is>
-          <t>Passed all criteria: Tech niche, 62,000 followers (within 5k-100k), 7.4% engagement, recently active.</t>
+          <t>Passed all criteria: Tech niche, 71,200 followers (within 5k-100k), 4.3% engagement, recently active.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Maya Tech Reviews</t>
+          <t>Prompt Engineering (Ehsan)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -3627,15 +3603,15 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@MayaTechReviews</t>
+          <t>https://www.youtube.com/@PromptEngineeringChannel</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>61400</v>
+        <v>69400</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -3645,37 +3621,37 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Developer Hardware, Ergonomics, Keyboards, Workstations</t>
+          <t>Prompt Engineering, Open Source LLMs, Ollama, Fine-Tuning</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>partnerships@mayatech.co</t>
+          <t>promptengineering.business@gmail.com</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>@mayatech</t>
+          <t>@prompt_eng</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>https://mayatech.co</t>
+          <t>https://github.com/promptengineering</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>22-39</t>
+          <t>20-35</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>70% Male, 30% Female</t>
+          <t>82% Male, 18% Female</t>
         </is>
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>US / Canada / Japan</t>
+          <t>US / India / Germany</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3685,14 +3661,14 @@
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>Passed all criteria: Tech niche, 61,400 followers (within 5k-100k), 6.0% engagement, recently active.</t>
+          <t>Passed all criteria: Tech niche, 69,400 followers (within 5k-100k), 5.9% engagement, recently active.</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>AI Decoded with Priya</t>
+          <t>OpenSourcePulse</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -3702,15 +3678,15 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@AIDecodedPriya</t>
+          <t>https://www.youtube.com/@OpenSourcePulse</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>58300</v>
+        <v>67800</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>5.0%</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -3720,37 +3696,37 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>LLMs, Transformers, NLP, PyTorch</t>
+          <t>Open Source, Linux, Self-Hosting, Privacy</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>priya.ai@researchhub.dev</t>
+          <t>collab@opensourcepulse.org</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>@priya_ai_dev</t>
+          <t>@ospulse</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>https://researchhub.dev/priya</t>
+          <t>https://opensourcepulse.org</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>21-36</t>
+          <t>23-45</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
         <is>
-          <t>74% Male, 26% Female</t>
+          <t>87% Male, 13% Female</t>
         </is>
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>India / US / UK</t>
+          <t>Germany / US / France</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -3760,14 +3736,14 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>Passed all criteria: Tech niche, 58,300 followers (within 5k-100k), 6.3% engagement, recently active.</t>
+          <t>Passed all criteria: Tech niche, 67,800 followers (within 5k-100k), 5.0% engagement, recently active.</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Kubernetes Explorer</t>
+          <t>PromptLab with Leo</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -3777,15 +3753,15 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@KubernetesExplorer</t>
+          <t>https://www.youtube.com/@PromptLabLeo</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>57800</v>
+        <v>63900</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -3795,37 +3771,37 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Kubernetes, Helm, K9s, Cloud Native</t>
+          <t>AI Agents, CrewAI, LangGraph, Multi-Agent Systems</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>support@k8sexplorer.dev</t>
+          <t>leo@promptlab.ai</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>@k8sexplorer</t>
+          <t>@promptlableo</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
         <is>
-          <t>https://k8sexplorer.dev</t>
+          <t>https://promptlab.ai</t>
         </is>
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>26-44</t>
+          <t>21-37</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>89% Male, 11% Female</t>
+          <t>81% Male, 19% Female</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>US / Germany / India</t>
+          <t>US / UK / Canada</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -3835,14 +3811,14 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>Passed all criteria: Tech niche, 57,800 followers (within 5k-100k), 4.7% engagement, recently active.</t>
+          <t>Passed all criteria: Tech niche, 63,900 followers (within 5k-100k), 6.7% engagement, recently active.</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Database Internals (Dmitri)</t>
+          <t>IndieDev Vlogs (Sam)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -3852,15 +3828,15 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@DatabaseInternalsDmitri</t>
+          <t>https://www.youtube.com/@SamIndieDev</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>55800</v>
+        <v>62000</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>7.4%</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -3870,37 +3846,37 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>PostgreSQL, B-Trees, Write Ahead Logs, Storage Engines</t>
+          <t>Indie Hacking, SaaS, Next.js, Supabase, Stripe</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>dmitri@dbinternals.net</t>
+          <t>sam@buildinpublic.xyz</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>@dmitridb</t>
+          <t>@sambuilds</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>https://dbinternals.net</t>
+          <t>https://buildinpublic.xyz</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>26-48</t>
+          <t>21-36</t>
         </is>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>90% Male, 10% Female</t>
+          <t>78% Male, 22% Female</t>
         </is>
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>US / Germany / Ukraine</t>
+          <t>US / UK / Netherlands</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -3910,14 +3886,14 @@
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>Passed all criteria: Tech niche, 55,800 followers (within 5k-100k), 4.8% engagement, recently active.</t>
+          <t>Passed all criteria: Tech niche, 62,000 followers (within 5k-100k), 7.4% engagement, recently active.</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Lucas AI Systems</t>
+          <t>Maya Tech Reviews</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -3927,15 +3903,15 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@LucasAISystems</t>
+          <t>https://www.youtube.com/@MayaTechReviews</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>52100</v>
+        <v>61400</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>5.8%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -3945,37 +3921,37 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Computer Vision, PyTorch, Autonomous Systems, YOLOv8</t>
+          <t>Developer Hardware, Ergonomics, Keyboards, Workstations</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>lucas@aivisionlabs.org</t>
+          <t>partnerships@mayatech.co</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>@lucas_vision</t>
+          <t>@mayatech</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
         <is>
-          <t>https://aivisionlabs.org</t>
+          <t>https://mayatech.co</t>
         </is>
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>22-38</t>
+          <t>22-39</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>81% Male, 19% Female</t>
+          <t>70% Male, 30% Female</t>
         </is>
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>US / Sweden / India</t>
+          <t>US / Canada / Japan</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -3985,14 +3961,14 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>Passed all criteria: Tech niche, 52,100 followers (within 5k-100k), 5.8% engagement, recently active.</t>
+          <t>Passed all criteria: Tech niche, 61,400 followers (within 5k-100k), 6.0% engagement, recently active.</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Tariq Flutter Hub</t>
+          <t>AI Decoded with Priya</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -4002,15 +3978,15 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@TariqFlutterHub</t>
+          <t>https://www.youtube.com/@AIDecodedPriya</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>51900</v>
+        <v>58300</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -4020,54 +3996,54 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Flutter, Dart, Mobile Dev, BLoC Pattern</t>
+          <t>LLMs, Transformers, NLP, PyTorch</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>tariq@flutterhub.io</t>
+          <t>priya.ai@researchhub.dev</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>@tariqflutter</t>
+          <t>@priya_ai_dev</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
         <is>
-          <t>https://flutterhub.io</t>
+          <t>https://researchhub.dev/priya</t>
         </is>
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>20-33</t>
+          <t>21-36</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>82% Male, 18% Female</t>
+          <t>74% Male, 26% Female</t>
         </is>
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Pakistan / UK / UAE</t>
+          <t>India / US / UK</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>FAILED</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>Content relevance: No verified tech / software developer keywords found in recent content or bio</t>
+          <t>Passed all criteria: Tech niche, 58,300 followers (within 5k-100k), 6.3% engagement, recently active.</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Hamza Coding</t>
+          <t>Kubernetes Explorer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -4077,15 +4053,15 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@HamzaCoding</t>
+          <t>https://www.youtube.com/@KubernetesExplorer</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>49000</v>
+        <v>57800</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>4.9%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -4095,27 +4071,27 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Go, Microservices, gRPC, PostgreSQL</t>
+          <t>Kubernetes, Helm, K9s, Cloud Native</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>hamza.dev@proton.me</t>
+          <t>support@k8sexplorer.dev</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>@hamzadev</t>
+          <t>@k8sexplorer</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>https://hamza.dev</t>
+          <t>https://k8sexplorer.dev</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>21-36</t>
+          <t>26-44</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4125,7 +4101,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Egypt / UAE / Germany</t>
+          <t>US / Germany / India</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4135,14 +4111,14 @@
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>Passed all criteria: Tech niche, 49,000 followers (within 5k-100k), 4.9% engagement, recently active.</t>
+          <t>Passed all criteria: Tech niche, 57,800 followers (within 5k-100k), 4.7% engagement, recently active.</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>RustInPractice</t>
+          <t>Database Internals (Dmitri)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -4152,15 +4128,15 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@RustInPractice</t>
+          <t>https://www.youtube.com/@DatabaseInternalsDmitri</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>48300</v>
+        <v>55800</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>5.4%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -4170,37 +4146,37 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Rust, Tokio, Networking, CLI Tools</t>
+          <t>PostgreSQL, B-Trees, Write Ahead Logs, Storage Engines</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>rustinpractice@pm.me</t>
+          <t>dmitri@dbinternals.net</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>@rustinpractice</t>
+          <t>@dmitridb</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>https://dbinternals.net</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>23-39</t>
+          <t>26-48</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>88% Male, 12% Female</t>
+          <t>90% Male, 10% Female</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>US / Germany / UK</t>
+          <t>US / Germany / Ukraine</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4210,14 +4186,14 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>Passed all criteria: Tech niche, 48,300 followers (within 5k-100k), 5.4% engagement, recently active.</t>
+          <t>Passed all criteria: Tech niche, 55,800 followers (within 5k-100k), 4.8% engagement, recently active.</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Alex Golang Lab</t>
+          <t>Lucas AI Systems</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -4227,15 +4203,15 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@AlexGolangLab</t>
+          <t>https://www.youtube.com/@LucasAISystems</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>47200</v>
+        <v>52100</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -4245,37 +4221,37 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Go, Concurrency, Goroutines, Distributed Systems</t>
+          <t>Computer Vision, PyTorch, Autonomous Systems, YOLOv8</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>alex@golanglab.io</t>
+          <t>lucas@aivisionlabs.org</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>@alexgolang</t>
+          <t>@lucas_vision</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>https://golanglab.io</t>
+          <t>https://aivisionlabs.org</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>24-40</t>
+          <t>22-38</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>89% Male, 11% Female</t>
+          <t>81% Male, 19% Female</t>
         </is>
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Germany / Russia / US</t>
+          <t>US / Sweden / India</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4285,14 +4261,14 @@
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>Passed all criteria: Tech niche, 47,200 followers (within 5k-100k), 5.1% engagement, recently active.</t>
+          <t>Passed all criteria: Tech niche, 52,100 followers (within 5k-100k), 5.8% engagement, recently active.</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Nate Data Engineering</t>
+          <t>Tariq Flutter Hub</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -4302,15 +4278,15 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@NateDataEngineering</t>
+          <t>https://www.youtube.com/@TariqFlutterHub</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>44300</v>
+        <v>51900</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>4.7%</t>
+          <t>5.2%</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -4320,54 +4296,54 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Apache Spark, Snowflake, dbt, Data Modeling</t>
+          <t>Flutter, Dart, Mobile Dev, BLoC Pattern</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>nate@dataengineeringweekly.com</t>
+          <t>tariq@flutterhub.io</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>@natedata</t>
+          <t>@tariqflutter</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>https://dataengineeringweekly.com</t>
+          <t>https://flutterhub.io</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>25-42</t>
+          <t>20-33</t>
         </is>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>84% Male, 16% Female</t>
+          <t>82% Male, 18% Female</t>
         </is>
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>US / UK / Australia</t>
+          <t>Pakistan / UK / UAE</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>PASSED</t>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>Passed all criteria: Tech niche, 44,300 followers (within 5k-100k), 4.7% engagement, recently active.</t>
+          <t>Content relevance: No verified tech / software developer keywords found in recent content or bio</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Gate Smashers</t>
+          <t>Hamza Coding</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -4377,15 +4353,15 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@GateSmashers</t>
+          <t>https://www.youtube.com/@HamzaCoding</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>43700</v>
+        <v>49000</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>1.5%</t>
+          <t>4.9%</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -4395,38 +4371,54 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Fastapi, AI</t>
+          <t>Go, Microservices, gRPC, PostgreSQL</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Not Found</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
-      <c r="J59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
+          <t>hamza.dev@proton.me</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>@hamzadev</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>https://hamza.dev</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>21-36</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>89% Male, 11% Female</t>
+        </is>
+      </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Egypt / UAE / Germany</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>FAILED</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>Engagement rate (1.5%) is below minimum healthy baseline of 2.0%</t>
+          <t>Passed all criteria: Tech niche, 49,000 followers (within 5k-100k), 4.9% engagement, recently active.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AI Engineer Diary (Marta)</t>
+          <t>RustInPractice</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -4436,15 +4428,15 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@AIEngineerDiary</t>
+          <t>https://www.youtube.com/@RustInPractice</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>43500</v>
+        <v>48300</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -4454,37 +4446,37 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>LLMOps, Evaluation, Prompt Engineering, Python</t>
+          <t>Rust, Tokio, Networking, CLI Tools</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>marta@aiengineerdiary.dev</t>
+          <t>rustinpractice@pm.me</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>@marta_ai</t>
+          <t>@rustinpractice</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>https://aiengineerdiary.dev</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>22-36</t>
+          <t>23-39</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>71% Male, 29% Female</t>
+          <t>88% Male, 12% Female</t>
         </is>
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Poland / Germany / US</t>
+          <t>US / Germany / UK</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4494,14 +4486,14 @@
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>Passed all criteria: Tech niche, 43,500 followers (within 5k-100k), 6.8% engagement, recently active.</t>
+          <t>Passed all criteria: Tech niche, 48,300 followers (within 5k-100k), 5.4% engagement, recently active.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Cosden Solutions</t>
+          <t>Alex Golang Lab</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -4511,15 +4503,15 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@CosdenSolutions</t>
+          <t>https://www.youtube.com/@AlexGolangLab</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>41800</v>
+        <v>47200</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -4529,37 +4521,37 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>React, Clean Code, Design Patterns, TypeScript</t>
+          <t>Go, Concurrency, Goroutines, Distributed Systems</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>contact@cosdensolutions.com</t>
+          <t>alex@golanglab.io</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>@cosdensolutions</t>
+          <t>@alexgolang</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
         <is>
-          <t>https://cosdensolutions.com</t>
+          <t>https://golanglab.io</t>
         </is>
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>21-35</t>
+          <t>24-40</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>79% Male, 21% Female</t>
+          <t>89% Male, 11% Female</t>
         </is>
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>UK / US / Australia</t>
+          <t>Germany / Russia / US</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4569,14 +4561,14 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>Passed all criteria: Tech niche, 41,800 followers (within 5k-100k), 7.1% engagement, recently active.</t>
+          <t>Passed all criteria: Tech niche, 47,200 followers (within 5k-100k), 5.1% engagement, recently active.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>ZeroTrust Architecture</t>
+          <t>Nate Data Engineering</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -4586,15 +4578,15 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@ZeroTrustArchitecture</t>
+          <t>https://www.youtube.com/@NateDataEngineering</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>41200</v>
+        <v>44300</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -4604,37 +4596,37 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Identity Management, OAuth2, OIDC, Security</t>
+          <t>Apache Spark, Snowflake, dbt, Data Modeling</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>contact@zerotrustarch.org</t>
+          <t>nate@dataengineeringweekly.com</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>@zerotrustarch</t>
+          <t>@natedata</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
         <is>
-          <t>https://zerotrustarch.org</t>
+          <t>https://dataengineeringweekly.com</t>
         </is>
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>27-48</t>
+          <t>25-42</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
         <is>
-          <t>86% Male, 14% Female</t>
+          <t>84% Male, 16% Female</t>
         </is>
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>US / UK / Switzerland</t>
+          <t>US / UK / Australia</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4644,14 +4636,14 @@
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>Passed all criteria: Tech niche, 41,200 followers (within 5k-100k), 4.3% engagement, recently active.</t>
+          <t>Passed all criteria: Tech niche, 44,300 followers (within 5k-100k), 4.7% engagement, recently active.</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Karan DevOps Lab</t>
+          <t>AI Engineer Diary (Marta)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -4661,15 +4653,15 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@KaranDevOpsLab</t>
+          <t>https://www.youtube.com/@AIEngineerDiary</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>38700</v>
+        <v>43500</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>4.6%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -4679,37 +4671,37 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Jenkins, GitHub Actions, AWS EKS, Terraform</t>
+          <t>LLMOps, Evaluation, Prompt Engineering, Python</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>karan.devops@gmail.com</t>
+          <t>marta@aiengineerdiary.dev</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>@karandevops</t>
+          <t>@marta_ai</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>https://aiengineerdiary.dev</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>22-35</t>
+          <t>22-36</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>86% Male, 14% Female</t>
+          <t>71% Male, 29% Female</t>
         </is>
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>India / US / Singapore</t>
+          <t>Poland / Germany / US</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
@@ -4719,14 +4711,14 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>Passed all criteria: Tech niche, 38,700 followers (within 5k-100k), 4.6% engagement, recently active.</t>
+          <t>Passed all criteria: Tech niche, 43,500 followers (within 5k-100k), 6.8% engagement, recently active.</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Chloe Frontend Journey</t>
+          <t>Cosden Solutions</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -4736,15 +4728,15 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@ChloeFrontendJourney</t>
+          <t>https://www.youtube.com/@CosdenSolutions</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>38400</v>
+        <v>41800</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>7.1%</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -4754,37 +4746,37 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>CSS Architecture, Figma to Code, React, Next.js</t>
+          <t>React, Clean Code, Design Patterns, TypeScript</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>chloe@frontendjourney.com</t>
+          <t>contact@cosdensolutions.com</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>@chloefrontend</t>
+          <t>@cosdensolutions</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
         <is>
-          <t>https://frontendjourney.com</t>
+          <t>https://cosdensolutions.com</t>
         </is>
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>19-33</t>
+          <t>21-35</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>66% Male, 34% Female</t>
+          <t>79% Male, 21% Female</t>
         </is>
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>US / Canada / Australia</t>
+          <t>UK / US / Australia</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
@@ -4794,14 +4786,14 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>Passed all criteria: Tech niche, 38,400 followers (within 5k-100k), 5.5% engagement, recently active.</t>
+          <t>Passed all criteria: Tech niche, 41,800 followers (within 5k-100k), 7.1% engagement, recently active.</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Mobile Architecture with Ken</t>
+          <t>ZeroTrust Architecture</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -4811,15 +4803,15 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@MobileArchKen</t>
+          <t>https://www.youtube.com/@ZeroTrustArchitecture</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>37100</v>
+        <v>41200</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -4829,54 +4821,54 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>iOS, SwiftUI, Combine, Clean Architecture</t>
+          <t>Identity Management, OAuth2, OIDC, Security</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>ken@swiftarch.dev</t>
+          <t>contact@zerotrustarch.org</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>@ken_swift</t>
+          <t>@zerotrustarch</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
         <is>
-          <t>https://swiftarch.dev</t>
+          <t>https://zerotrustarch.org</t>
         </is>
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>22-38</t>
+          <t>27-48</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>80% Male, 20% Female</t>
+          <t>86% Male, 14% Female</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>US / Japan / UK</t>
+          <t>US / UK / Switzerland</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>FAILED</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>Content relevance: No verified tech / software developer keywords found in recent content or bio</t>
+          <t>Passed all criteria: Tech niche, 41,200 followers (within 5k-100k), 4.3% engagement, recently active.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>NeoVim Made Easy</t>
+          <t>Karan DevOps Lab</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -4886,15 +4878,15 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@NeoVimMadeEasy</t>
+          <t>https://www.youtube.com/@KaranDevOpsLab</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>36700</v>
+        <v>38700</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>4.6%</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -4904,54 +4896,54 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Neovim, Lua, Productivity, Terminal Workflows</t>
+          <t>Jenkins, GitHub Actions, AWS EKS, Terraform</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>neovim.easy@gmail.com</t>
+          <t>karan.devops@gmail.com</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>@neovimeasy</t>
+          <t>@karandevops</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>https://github.com/neovimeasy</t>
+          <t>None</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>19-35</t>
+          <t>22-35</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
         <is>
-          <t>85% Male, 15% Female</t>
+          <t>86% Male, 14% Female</t>
         </is>
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>US / UK / Sweden</t>
+          <t>India / US / Singapore</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>FAILED</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>Content relevance: No verified tech / software developer keywords found in recent content or bio</t>
+          <t>Passed all criteria: Tech niche, 38,700 followers (within 5k-100k), 4.6% engagement, recently active.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Elena Codes</t>
+          <t>Chloe Frontend Journey</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -4961,15 +4953,15 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@ElenaCodesTech</t>
+          <t>https://www.youtube.com/@ChloeFrontendJourney</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>35600</v>
+        <v>38400</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -4979,37 +4971,37 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Frontend, Vue.js, CSS Animations, UI/UX Development</t>
+          <t>CSS Architecture, Figma to Code, React, Next.js</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>elena@elenacodes.io</t>
+          <t>chloe@frontendjourney.com</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>@elenacodes</t>
+          <t>@chloefrontend</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>https://elenacodes.io</t>
+          <t>https://frontendjourney.com</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>19-32</t>
+          <t>19-33</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
         <is>
-          <t>64% Male, 36% Female</t>
+          <t>66% Male, 34% Female</t>
         </is>
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>UK / Germany / Spain</t>
+          <t>US / Canada / Australia</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5019,14 +5011,14 @@
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>Passed all criteria: Tech niche, 35,600 followers (within 5k-100k), 6.4% engagement, recently active.</t>
+          <t>Passed all criteria: Tech niche, 38,400 followers (within 5k-100k), 5.5% engagement, recently active.</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>DevSecOps Insights</t>
+          <t>Mobile Architecture with Ken</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -5036,15 +5028,15 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@DevSecOpsInsights</t>
+          <t>https://www.youtube.com/@MobileArchKen</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>34100</v>
+        <v>37100</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>4.0%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -5054,54 +5046,54 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Application Security, SAST / DAST, Container Security, OWASP</t>
+          <t>iOS, SwiftUI, Combine, Clean Architecture</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>team@devsecopsinsights.org</t>
+          <t>ken@swiftarch.dev</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>@devsecinsights</t>
+          <t>@ken_swift</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>https://devsecopsinsights.org</t>
+          <t>https://swiftarch.dev</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>26-44</t>
+          <t>22-38</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>85% Male, 15% Female</t>
+          <t>80% Male, 20% Female</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>US / UK / India</t>
+          <t>US / Japan / UK</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>PASSED</t>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>Passed all criteria: Tech niche, 34,100 followers (within 5k-100k), 4.0% engagement, recently active.</t>
+          <t>Content relevance: No verified tech / software developer keywords found in recent content or bio</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Marcus Cloud Native</t>
+          <t>NeoVim Made Easy</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -5111,15 +5103,15 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@MarcusCloudNative</t>
+          <t>https://www.youtube.com/@NeoVimMadeEasy</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>32900</v>
+        <v>36700</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>4.4%</t>
+          <t>6.0%</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -5129,32 +5121,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Terraform, Google Cloud, Istio Service Mesh, DevSecOps</t>
+          <t>Neovim, Lua, Productivity, Terminal Workflows</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>marcus@cloudnativehq.com</t>
+          <t>neovim.easy@gmail.com</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>@marcuscloud</t>
+          <t>@neovimeasy</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>https://cloudnativehq.com</t>
+          <t>https://github.com/neovimeasy</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>27-46</t>
+          <t>19-35</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>88% Male, 12% Female</t>
+          <t>85% Male, 15% Female</t>
         </is>
       </c>
       <c r="M69" t="inlineStr">
@@ -5164,19 +5156,19 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>PASSED</t>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>Passed all criteria: Tech niche, 32,900 followers (within 5k-100k), 4.4% engagement, recently active.</t>
+          <t>Content relevance: No verified tech / software developer keywords found in recent content or bio</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>TestDriven Dev (Liam)</t>
+          <t>Elena Codes</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -5186,15 +5178,15 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@TestDrivenDevLiam</t>
+          <t>https://www.youtube.com/@ElenaCodesTech</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>31500</v>
+        <v>35600</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -5204,37 +5196,37 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>TDD, PyTest, Jest, Software Quality</t>
+          <t>Frontend, Vue.js, CSS Animations, UI/UX Development</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>liam@testdrivendev.com</t>
+          <t>elena@elenacodes.io</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>@liam_tdd</t>
+          <t>@elenacodes</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>https://testdrivendev.com</t>
+          <t>https://elenacodes.io</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>25-42</t>
+          <t>19-32</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>82% Male, 18% Female</t>
+          <t>64% Male, 36% Female</t>
         </is>
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>UK / US / Canada</t>
+          <t>UK / Germany / Spain</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5244,14 +5236,14 @@
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>Passed all criteria: Tech niche, 31,500 followers (within 5k-100k), 4.5% engagement, recently active.</t>
+          <t>Passed all criteria: Tech niche, 35,600 followers (within 5k-100k), 6.4% engagement, recently active.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Shaw Talebi</t>
+          <t>DevSecOps Insights</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -5261,15 +5253,15 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@shawnhiman</t>
+          <t>https://www.youtube.com/@DevSecOpsInsights</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>31200</v>
+        <v>34100</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>4.0%</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -5279,32 +5271,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Data Science, Math for ML, Python, Physics</t>
+          <t>Application Security, SAST / DAST, Container Security, OWASP</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>shaw@shawtalebi.com</t>
+          <t>team@devsecopsinsights.org</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>@shawtalebi</t>
+          <t>@devsecinsights</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>https://shawtalebi.com</t>
+          <t>https://devsecopsinsights.org</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>19-32</t>
+          <t>26-44</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
         <is>
-          <t>76% Male, 24% Female</t>
+          <t>85% Male, 15% Female</t>
         </is>
       </c>
       <c r="M71" t="inlineStr">
@@ -5319,14 +5311,14 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>Passed all criteria: Tech niche, 31,200 followers (within 5k-100k), 6.2% engagement, recently active.</t>
+          <t>Passed all criteria: Tech niche, 34,100 followers (within 5k-100k), 4.0% engagement, recently active.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>FastAPI Master</t>
+          <t>Marcus Cloud Native</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -5336,15 +5328,15 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@FastAPIMaster</t>
+          <t>https://www.youtube.com/@MarcusCloudNative</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>29600</v>
+        <v>32900</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>4.4%</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -5354,37 +5346,37 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>FastAPI, Pydantic, SQLAlchemy, Asyncio Python</t>
+          <t>Terraform, Google Cloud, Istio Service Mesh, DevSecOps</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>support@fastapimaster.dev</t>
+          <t>marcus@cloudnativehq.com</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>@fastapimaster</t>
+          <t>@marcuscloud</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
         <is>
-          <t>https://fastapimaster.dev</t>
+          <t>https://cloudnativehq.com</t>
         </is>
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>22-38</t>
+          <t>27-46</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>83% Male, 17% Female</t>
+          <t>88% Male, 12% Female</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>US / Brazil / Germany</t>
+          <t>US / UK / Sweden</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5394,14 +5386,14 @@
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>Passed all criteria: Tech niche, 29,600 followers (within 5k-100k), 5.3% engagement, recently active.</t>
+          <t>Passed all criteria: Tech niche, 32,900 followers (within 5k-100k), 4.4% engagement, recently active.</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Hannah CyberOps</t>
+          <t>TestDriven Dev (Liam)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -5411,15 +5403,15 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@HannahCyberOps</t>
+          <t>https://www.youtube.com/@TestDrivenDevLiam</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>29400</v>
+        <v>31500</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -5429,37 +5421,37 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Blue Team, SIEM, Splunk, Incident Response</t>
+          <t>TDD, PyTest, Jest, Software Quality</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>hannah@cyberopsacademy.io</t>
+          <t>liam@testdrivendev.com</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>@hannahcyber</t>
+          <t>@liam_tdd</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>https://cyberopsacademy.io</t>
+          <t>https://testdrivendev.com</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>22-38</t>
+          <t>25-42</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
         <is>
-          <t>72% Male, 28% Female</t>
+          <t>82% Male, 18% Female</t>
         </is>
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>US / UK / Germany</t>
+          <t>UK / US / Canada</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5469,14 +5461,14 @@
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>Passed all criteria: Tech niche, 29,400 followers (within 5k-100k), 6.2% engagement, recently active.</t>
+          <t>Passed all criteria: Tech niche, 31,500 followers (within 5k-100k), 4.5% engagement, recently active.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Design Systems with Rachel</t>
+          <t>Shaw Talebi</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -5486,15 +5478,15 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@DesignSystemsRachel</t>
+          <t>https://www.youtube.com/@shawnhiman</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>28900</v>
+        <v>31200</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -5504,37 +5496,37 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Design Systems, Storybook, React, Design Tokens</t>
+          <t>Data Science, Math for ML, Python, Physics</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>rachel@designsystems.io</t>
+          <t>shaw@shawtalebi.com</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>@rachel_designsys</t>
+          <t>@shawtalebi</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
         <is>
-          <t>https://designsystems.io</t>
+          <t>https://shawtalebi.com</t>
         </is>
       </c>
       <c r="K74" t="inlineStr">
         <is>
-          <t>21-36</t>
+          <t>19-32</t>
         </is>
       </c>
       <c r="L74" t="inlineStr">
         <is>
-          <t>65% Male, 35% Female</t>
+          <t>76% Male, 24% Female</t>
         </is>
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>US / UK / Germany</t>
+          <t>US / UK / India</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5544,14 +5536,14 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>Passed all criteria: Tech niche, 28,900 followers (within 5k-100k), 5.9% engagement, recently active.</t>
+          <t>Passed all criteria: Tech niche, 31,200 followers (within 5k-100k), 6.2% engagement, recently active.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Bapoulo DevOps</t>
+          <t>FastAPI Master</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -5561,15 +5553,15 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@BapouloDevOps</t>
+          <t>https://www.youtube.com/@FastAPIMaster</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>28400</v>
+        <v>29600</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>4.2%</t>
+          <t>5.3%</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -5579,37 +5571,37 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>DevOps, Kubernetes, Terraform, CI/CD, Docker</t>
+          <t>FastAPI, Pydantic, SQLAlchemy, Asyncio Python</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>bapoulo.devops@gmail.com</t>
+          <t>support@fastapimaster.dev</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>@bapoulodevops</t>
+          <t>@fastapimaster</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>https://fastapimaster.dev</t>
         </is>
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>24-40</t>
+          <t>22-38</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
         <is>
-          <t>88% Male, 12% Female</t>
+          <t>83% Male, 17% Female</t>
         </is>
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>France / US / India</t>
+          <t>US / Brazil / Germany</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5619,14 +5611,14 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>Passed all criteria: Tech niche, 28,400 followers (within 5k-100k), 4.2% engagement, recently active.</t>
+          <t>Passed all criteria: Tech niche, 29,600 followers (within 5k-100k), 5.3% engagement, recently active.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Matt Williams Cloud</t>
+          <t>Hannah CyberOps</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -5636,15 +5628,15 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@MattWilliamsCloud</t>
+          <t>https://www.youtube.com/@HannahCyberOps</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>27300</v>
+        <v>29400</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>3.7%</t>
+          <t>6.2%</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -5654,37 +5646,37 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Cloud Architecture, Linux, Containers, DevOps</t>
+          <t>Blue Team, SIEM, Splunk, Incident Response</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>matt@technovangelist.com</t>
+          <t>hannah@cyberopsacademy.io</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>@technovangelist</t>
+          <t>@hannahcyber</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>https://technovangelist.com</t>
+          <t>https://cyberopsacademy.io</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>26-44</t>
+          <t>22-38</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
         <is>
-          <t>86% Male, 14% Female</t>
+          <t>72% Male, 28% Female</t>
         </is>
       </c>
       <c r="M76" t="inlineStr">
         <is>
-          <t>US / Canada</t>
+          <t>US / UK / Germany</t>
         </is>
       </c>
       <c r="N76" t="inlineStr">
@@ -5694,14 +5686,14 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>Passed all criteria: Tech niche, 27,300 followers (within 5k-100k), 3.7% engagement, recently active.</t>
+          <t>Passed all criteria: Tech niche, 29,400 followers (within 5k-100k), 6.2% engagement, recently active.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>GraphQL Today</t>
+          <t>Design Systems with Rachel</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -5711,15 +5703,15 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@GraphQLToday</t>
+          <t>https://www.youtube.com/@DesignSystemsRachel</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>25800</v>
+        <v>28900</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>5.9%</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -5729,54 +5721,54 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>GraphQL, Apollo, Federation, TypeScript</t>
+          <t>Design Systems, Storybook, React, Design Tokens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>info@graphqltoday.com</t>
+          <t>rachel@designsystems.io</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>@graphqltoday</t>
+          <t>@rachel_designsys</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>https://graphqltoday.com</t>
+          <t>https://designsystems.io</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>24-40</t>
+          <t>21-36</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
         <is>
-          <t>81% Male, 19% Female</t>
+          <t>65% Male, 35% Female</t>
         </is>
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>US / France / India</t>
+          <t>US / UK / Germany</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>FAILED</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>Content relevance: No verified tech / software developer keywords found in recent content or bio</t>
+          <t>Passed all criteria: Tech niche, 28,900 followers (within 5k-100k), 5.9% engagement, recently active.</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>InactiveCloudGuy</t>
+          <t>Bapoulo DevOps</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -5786,15 +5778,15 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@InactiveCloudGuy</t>
+          <t>https://www.youtube.com/@BapouloDevOps</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>24000</v>
+        <v>28400</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -5804,17 +5796,17 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>AWS, Serverless, Terraform</t>
+          <t>DevOps, Kubernetes, Terraform, CI/CD, Docker</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>hello@cloudguyinactive.io</t>
+          <t>bapoulo.devops@gmail.com</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>@inactivecloud</t>
+          <t>@bapoulodevops</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -5829,29 +5821,29 @@
       </c>
       <c r="L78" t="inlineStr">
         <is>
-          <t>80% Male, 20% Female</t>
+          <t>88% Male, 12% Female</t>
         </is>
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>US</t>
+          <t>France / US / India</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>FAILED</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>Channel inactive: last published content was 210 days ago (exceeds 120 days)</t>
+          <t>Passed all criteria: Tech niche, 28,400 followers (within 5k-100k), 4.2% engagement, recently active.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Sophie WebDev</t>
+          <t>Matt Williams Cloud</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
@@ -5861,15 +5853,15 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@SophieWebDev</t>
+          <t>https://www.youtube.com/@MattWilliamsCloud</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>23100</v>
+        <v>27300</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>5.2%</t>
+          <t>3.7%</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -5879,37 +5871,37 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Web Components, Vanilla JS, Accessibility, Performance</t>
+          <t>Cloud Architecture, Linux, Containers, DevOps</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>sophie@webstandards.dev</t>
+          <t>matt@technovangelist.com</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>@sophieweb</t>
+          <t>@technovangelist</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
         <is>
-          <t>https://webstandards.dev</t>
+          <t>https://technovangelist.com</t>
         </is>
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>24-38</t>
+          <t>26-44</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
         <is>
-          <t>67% Male, 33% Female</t>
+          <t>86% Male, 14% Female</t>
         </is>
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>UK / Netherlands / US</t>
+          <t>US / Canada</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -5919,14 +5911,14 @@
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>Passed all criteria: Tech niche, 23,100 followers (within 5k-100k), 5.2% engagement, recently active.</t>
+          <t>Passed all criteria: Tech niche, 27,300 followers (within 5k-100k), 3.7% engagement, recently active.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Embedded with Jason</t>
+          <t>Mohit Decodes</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
@@ -5936,15 +5928,15 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@EmbeddedWithJason</t>
+          <t>https://www.youtube.com/@MohitDecodes</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>22400</v>
+        <v>26300</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>1.5%</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -5954,54 +5946,46 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Embedded C, STM32, FreeRTOS, IoT</t>
+          <t>Fastapi</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>jason@embeddedcorner.dev</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>@jasonembedded</t>
-        </is>
-      </c>
-      <c r="J80" t="inlineStr">
-        <is>
-          <t>https://embeddedcorner.dev</t>
-        </is>
-      </c>
+          <t>mohitdecodes@gmail.com</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr">
         <is>
-          <t>24-42</t>
+          <t>18-34</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
         <is>
-          <t>89% Male, 11% Female</t>
+          <t>Mixed</t>
         </is>
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>US / Germany / Japan</t>
+          <t>Global</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>PASSED</t>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>Passed all criteria: Tech niche, 22,400 followers (within 5k-100k), 4.1% engagement, recently active.</t>
+          <t>Engagement rate (1.5%) is below minimum healthy baseline of 2.0%</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>SvelteCraft</t>
+          <t>GraphQL Today</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
@@ -6011,15 +5995,15 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@SvelteCraft</t>
+          <t>https://www.youtube.com/@GraphQLToday</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>21500</v>
+        <v>25800</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>5.7%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -6029,54 +6013,54 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Svelte, SvelteKit, Tailwind CSS, Full Stack</t>
+          <t>GraphQL, Apollo, Federation, TypeScript</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>hello@sveltecraft.com</t>
+          <t>info@graphqltoday.com</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>@sveltecraft</t>
+          <t>@graphqltoday</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>https://sveltecraft.com</t>
+          <t>https://graphqltoday.com</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>21-36</t>
+          <t>24-40</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
         <is>
-          <t>77% Male, 23% Female</t>
+          <t>81% Male, 19% Female</t>
         </is>
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>US / UK / France</t>
+          <t>US / France / India</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>PASSED</t>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>Passed all criteria: Tech niche, 21,500 followers (within 5k-100k), 5.7% engagement, recently active.</t>
+          <t>Content relevance: No verified tech / software developer keywords found in recent content or bio</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Sara Backend Chronicles</t>
+          <t>InactiveCloudGuy</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
@@ -6086,15 +6070,15 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@SaraBackendChronicles</t>
+          <t>https://www.youtube.com/@InactiveCloudGuy</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>19800</v>
+        <v>24000</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>6.1%</t>
+          <t>3.8%</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -6104,17 +6088,17 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Node.js, Express, MongoDB, System Design</t>
+          <t>AWS, Serverless, Terraform</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>sara.backend@techmail.io</t>
+          <t>hello@cloudguyinactive.io</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>@sarabackend</t>
+          <t>@inactivecloud</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -6124,34 +6108,34 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>20-34</t>
+          <t>24-40</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
         <is>
-          <t>71% Male, 29% Female</t>
+          <t>80% Male, 20% Female</t>
         </is>
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Canada / US / UK</t>
+          <t>US</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>PASSED</t>
+          <t>FAILED</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>Passed all criteria: Tech niche, 19,800 followers (within 5k-100k), 6.1% engagement, recently active.</t>
+          <t>Channel inactive: last published content was 210 days ago (exceeds 120 days)</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Gabe's Coding Corner</t>
+          <t>Sophie WebDev</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
@@ -6161,15 +6145,15 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@GabeCodingCorner</t>
+          <t>https://www.youtube.com/@SophieWebDev</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>18900</v>
+        <v>23100</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>5.2%</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -6179,37 +6163,37 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Rust, Embedded Systems, WebAssembly, C</t>
+          <t>Web Components, Vanilla JS, Accessibility, Performance</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Not Found</t>
+          <t>sophie@webstandards.dev</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>@gabecodes</t>
+          <t>@sophieweb</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
         <is>
-          <t>https://gabecodes.dev</t>
+          <t>https://webstandards.dev</t>
         </is>
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>22-36</t>
+          <t>24-38</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
         <is>
-          <t>87% Male, 13% Female</t>
+          <t>67% Male, 33% Female</t>
         </is>
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Germany / Netherlands / US</t>
+          <t>UK / Netherlands / US</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6219,14 +6203,14 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>Passed all criteria: Tech niche, 18,900 followers (within 5k-100k), 4.5% engagement, recently active.</t>
+          <t>Passed all criteria: Tech niche, 23,100 followers (within 5k-100k), 5.2% engagement, recently active.</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>ByteSize DevOps</t>
+          <t>Embedded with Jason</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
@@ -6236,15 +6220,15 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@ByteSizeDevOps</t>
+          <t>https://www.youtube.com/@EmbeddedWithJason</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>16200</v>
+        <v>22400</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>4.3%</t>
+          <t>4.1%</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -6254,37 +6238,37 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Docker, Linux Shell, Automation, Ansible</t>
+          <t>Embedded C, STM32, FreeRTOS, IoT</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>bytesizedevops@outlook.com</t>
+          <t>jason@embeddedcorner.dev</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>@bytesizedevops</t>
+          <t>@jasonembedded</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
         <is>
-          <t>None</t>
+          <t>https://embeddedcorner.dev</t>
         </is>
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>20-33</t>
+          <t>24-42</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>85% Male, 15% Female</t>
+          <t>89% Male, 11% Female</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>India / US / Poland</t>
+          <t>US / Germany / Japan</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6294,14 +6278,14 @@
       </c>
       <c r="O84" t="inlineStr">
         <is>
-          <t>Passed all criteria: Tech niche, 16,200 followers (within 5k-100k), 4.3% engagement, recently active.</t>
+          <t>Passed all criteria: Tech niche, 22,400 followers (within 5k-100k), 4.1% engagement, recently active.</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Pau Labarta Bajo</t>
+          <t>SvelteCraft</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
@@ -6311,15 +6295,15 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@paulabartabajo</t>
+          <t>https://www.youtube.com/@SvelteCraft</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>14200</v>
+        <v>21500</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>5.6%</t>
+          <t>5.7%</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -6329,37 +6313,37 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>MLOps, Feature Stores, Real-Time ML, Python, Hopsworks</t>
+          <t>Svelte, SvelteKit, Tailwind CSS, Full Stack</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>pau@realworldml.net</t>
+          <t>hello@sveltecraft.com</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>@paulabarta</t>
+          <t>@sveltecraft</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>https://realworldml.net</t>
+          <t>https://sveltecraft.com</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>25-38</t>
+          <t>21-36</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
         <is>
-          <t>83% Male, 17% Female</t>
+          <t>77% Male, 23% Female</t>
         </is>
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Spain / US / Germany</t>
+          <t>US / UK / France</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6369,14 +6353,14 @@
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>Passed all criteria: Tech niche, 14,200 followers (within 5k-100k), 5.6% engagement, recently active.</t>
+          <t>Passed all criteria: Tech niche, 21,500 followers (within 5k-100k), 5.7% engagement, recently active.</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Telusko</t>
+          <t>Sara Backend Chronicles</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
@@ -6386,15 +6370,15 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@Telusko</t>
+          <t>https://www.youtube.com/@SaraBackendChronicles</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>6820</v>
+        <v>19800</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>6.1%</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -6404,21 +6388,37 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Fastapi, Python, Web</t>
+          <t>Node.js, Express, MongoDB, System Design</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Not Found</t>
-        </is>
-      </c>
-      <c r="I86" t="inlineStr"/>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
+          <t>sara.backend@techmail.io</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr">
+        <is>
+          <t>@sarabackend</t>
+        </is>
+      </c>
+      <c r="J86" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K86" t="inlineStr">
+        <is>
+          <t>20-34</t>
+        </is>
+      </c>
+      <c r="L86" t="inlineStr">
+        <is>
+          <t>71% Male, 29% Female</t>
+        </is>
+      </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Canada / US / UK</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6428,14 +6428,14 @@
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>Passed all criteria: Tech niche, 6,820 followers (within 5k-100k), 9.5% engagement, recently active.</t>
+          <t>Passed all criteria: Tech niche, 19,800 followers (within 5k-100k), 6.1% engagement, recently active.</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Mohit Decodes</t>
+          <t>Gabe's Coding Corner</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
@@ -6445,15 +6445,15 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@MohitDecodes</t>
+          <t>https://www.youtube.com/@GabeCodingCorner</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>6500</v>
+        <v>18900</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>2.0%</t>
+          <t>4.5%</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -6463,21 +6463,37 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Fastapi</t>
+          <t>Rust, Embedded Systems, WebAssembly, C</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>mohitdecodes@gmail.com</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr"/>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>@gabecodes</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>https://gabecodes.dev</t>
+        </is>
+      </c>
+      <c r="K87" t="inlineStr">
+        <is>
+          <t>22-36</t>
+        </is>
+      </c>
+      <c r="L87" t="inlineStr">
+        <is>
+          <t>87% Male, 13% Female</t>
+        </is>
+      </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Germany / Netherlands / US</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6487,14 +6503,14 @@
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>Passed all criteria: Tech niche, 6,500 followers (within 5k-100k), 2.0% engagement, recently active.</t>
+          <t>Passed all criteria: Tech niche, 18,900 followers (within 5k-100k), 4.5% engagement, recently active.</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>CryptoCoderz</t>
+          <t>ByteSize DevOps</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -6504,35 +6520,35 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@CryptoCoderz</t>
+          <t>https://www.youtube.com/@ByteSizeDevOps</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>4100</v>
+        <v>16200</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>4.3%</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Technology</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Solidity, Smart Contracts, Web3</t>
+          <t>Docker, Linux Shell, Automation, Ansible</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>info@cryptocoderz.net</t>
+          <t>bytesizedevops@outlook.com</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>@cryptocoderz</t>
+          <t>@bytesizedevops</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -6542,100 +6558,309 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>18-30</t>
+          <t>20-33</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
         <is>
-          <t>92% Male, 8% Female</t>
+          <t>85% Male, 15% Female</t>
         </is>
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>India / US / Poland</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>FAILED</t>
+          <t>PASSED</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>Niche mismatch: 'Crypto' does not match target category 'Technology' | Subscribers/Followers (4,100) below micro-influencer floor of 5,000 | Engagement rate (1.9%) is below minimum healthy baseline of 2.0%</t>
+          <t>Passed all criteria: Tech niche, 16,200 followers (within 5k-100k), 4.3% engagement, recently active.</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
+          <t>Pau Labarta Bajo</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@paulabartabajo</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>14200</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>5.6%</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>MLOps, Feature Stores, Real-Time ML, Python, Hopsworks</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>pau@realworldml.net</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>@paulabarta</t>
+        </is>
+      </c>
+      <c r="J89" t="inlineStr">
+        <is>
+          <t>https://realworldml.net</t>
+        </is>
+      </c>
+      <c r="K89" t="inlineStr">
+        <is>
+          <t>25-38</t>
+        </is>
+      </c>
+      <c r="L89" t="inlineStr">
+        <is>
+          <t>83% Male, 17% Female</t>
+        </is>
+      </c>
+      <c r="M89" t="inlineStr">
+        <is>
+          <t>Spain / US / Germany</t>
+        </is>
+      </c>
+      <c r="N89" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="O89" t="inlineStr">
+        <is>
+          <t>Passed all criteria: Tech niche, 14,200 followers (within 5k-100k), 5.6% engagement, recently active.</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Telusko</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@Telusko</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>6820</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>9.5%</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Fastapi, Python, Web</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>Not Found</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="N90" t="inlineStr">
+        <is>
+          <t>PASSED</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr">
+        <is>
+          <t>Passed all criteria: Tech niche, 6,820 followers (within 5k-100k), 9.5% engagement, recently active.</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>CryptoCoderz</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>https://www.youtube.com/@CryptoCoderz</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>4100</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>1.9%</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Crypto</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Solidity, Smart Contracts, Web3</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>info@cryptocoderz.net</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>@cryptocoderz</t>
+        </is>
+      </c>
+      <c r="J91" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="K91" t="inlineStr">
+        <is>
+          <t>18-30</t>
+        </is>
+      </c>
+      <c r="L91" t="inlineStr">
+        <is>
+          <t>92% Male, 8% Female</t>
+        </is>
+      </c>
+      <c r="M91" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="N91" t="inlineStr">
+        <is>
+          <t>FAILED</t>
+        </is>
+      </c>
+      <c r="O91" t="inlineStr">
+        <is>
+          <t>Niche mismatch: 'Crypto' does not match target category 'Technology' | Subscribers/Followers (4,100) below micro-influencer floor of 5,000 | Engagement rate (1.9%) is below minimum healthy baseline of 2.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
           <t>BuggyCodeLab</t>
         </is>
       </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>YouTube</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>YouTube</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
         <is>
           <t>https://www.youtube.com/@BuggyCodeLab</t>
         </is>
       </c>
-      <c r="D89" t="n">
+      <c r="D92" t="n">
         <v>3200</v>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="E92" t="inlineStr">
         <is>
           <t>2.1%</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
         <is>
           <t>C++, Game Dev, OpenGL</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
+      <c r="H92" t="inlineStr">
         <is>
           <t>Not Found</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
+      <c r="I92" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="J89" t="inlineStr">
+      <c r="J92" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr">
+      <c r="K92" t="inlineStr">
         <is>
           <t>18-25</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr">
+      <c r="L92" t="inlineStr">
         <is>
           <t>90% Male, 10% Female</t>
         </is>
       </c>
-      <c r="M89" t="inlineStr">
+      <c r="M92" t="inlineStr">
         <is>
           <t>US</t>
         </is>
       </c>
-      <c r="N89" t="inlineStr">
+      <c r="N92" t="inlineStr">
         <is>
           <t>FAILED</t>
         </is>
       </c>
-      <c r="O89" t="inlineStr">
+      <c r="O92" t="inlineStr">
         <is>
           <t>Subscribers/Followers (3,200) below micro-influencer floor of 5,000</t>
         </is>
